--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -95,7 +95,10 @@
     <t>5J7X9S3</t>
   </si>
   <si>
-    <t>Resguardo impreso solo para observación</t>
+    <t>fdafsdf</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00162</t>
   </si>
   <si>
     <t>Cargador Laptop</t>
@@ -846,7 +849,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="9">
-        <v>45769.0</v>
+        <v>45770.0</v>
       </c>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="15">
@@ -1013,42 +1016,34 @@
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22">
-        <v>2</v>
-      </c>
-      <c r="B20" s="22" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>27</v>
-      </c>
       <c r="E20" s="22"/>
-      <c r="F20" s="22" t="s">
-        <v>28</v>
-      </c>
+      <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
       <c r="A21" s="22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C21" s="22" t="s">
         <v>22</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
@@ -1056,20 +1051,20 @@
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
@@ -1077,20 +1072,20 @@
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
       <c r="A23" s="22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
@@ -1098,83 +1093,91 @@
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
       <c r="A24" s="22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24" s="22" t="s">
         <v>22</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
+      <c r="A25" s="22">
+        <v>6</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
       <c r="A30" s="28" t="s">
@@ -1202,144 +1205,141 @@
       <c r="H31" s="28"/>
       <c r="I31" s="28"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A32" s="29" t="s">
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="27">
-      <c r="A33" s="28" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A33" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="39">
-      <c r="A35" s="31" t="s">
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="27">
+      <c r="A34" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="39">
+      <c r="A36" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="33"/>
       <c r="I37" s="33"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="32"/>
-      <c r="B38" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="2"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="15">
+      <c r="A39" s="32"/>
+      <c r="B39" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
-        <v>51</v>
-      </c>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="G39" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="36" t="s">
+        <v>52</v>
+      </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="34" t="str">
-        <f>C10</f>
-        <v>Juan Carlos Requena</v>
-      </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
@@ -1351,22 +1351,27 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="34" t="str">
+        <f>C10</f>
+        <v>Juan Carlos Requena</v>
+      </c>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="34" t="str">
         <f>C12</f>
         <v>Programador Junior</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
@@ -1375,20 +1380,31 @@
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="32"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1407,23 +1423,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G39:I39"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="G43:I43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1442,11 +1458,14 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H19:I25"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>
-  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -95,7 +95,7 @@
     <t>5J7X9S3</t>
   </si>
   <si>
-    <t>Resguardo impreso solo para observación</t>
+    <t>dkjmbn,jm</t>
   </si>
   <si>
     <t>Cargador Laptop</t>
@@ -846,7 +846,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="9">
-        <v>45769.0</v>
+        <v>45770.0</v>
       </c>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="15">

--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -38,6 +38,9 @@
     <t>Fecha:</t>
   </si>
   <si>
+    <t>23/04/2025</t>
+  </si>
+  <si>
     <t>Nombre:</t>
   </si>
   <si>
@@ -93,9 +96,6 @@
   </si>
   <si>
     <t>5J7X9S3</t>
-  </si>
-  <si>
-    <t>dtdft</t>
   </si>
   <si>
     <t>DVZ-VH-TI-00162</t>
@@ -852,8 +852,8 @@
       <c r="H8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="9">
-        <v>45770.0</v>
+      <c r="I8" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="15">
@@ -869,11 +869,11 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="15">
       <c r="A10" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -896,23 +896,23 @@
     <row r="12" spans="1:10" customHeight="1" ht="15">
       <c r="A12" s="2"/>
       <c r="B12" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="18"/>
     </row>
@@ -929,7 +929,7 @@
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="15">
       <c r="A14" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -975,24 +975,24 @@
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="15">
       <c r="A18" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="22"/>
     </row>
@@ -1001,22 +1001,20 @@
         <v>1</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" s="38"/>
       <c r="F19" s="38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
-        <v>25</v>
-      </c>
+      <c r="H19" s="38"/>
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
@@ -1040,7 +1038,7 @@
         <v>27</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="38" t="s">
         <v>28</v>
@@ -1061,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>31</v>
@@ -1103,7 +1101,7 @@
         <v>37</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>38</v>
@@ -1124,7 +1122,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>41</v>

--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>23/04/2025</t>
+    <t>28/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>

--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>28/04/2025</t>
+    <t>30/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Tampico</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Supervisor TI</t>
+    <t>Rednar García Harcía</t>
+  </si>
+  <si>
+    <t>Auxiliar de Supervision</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/04/2025</t>
+    <t>08/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Tampico</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -101,7 +101,7 @@
     <t>DVZ-VH-TI-00162</t>
   </si>
   <si>
-    <t>Cargador Laptop</t>
+    <t>Cargador de Laptop</t>
   </si>
   <si>
     <t>LA65NM190</t>
@@ -119,7 +119,7 @@
     <t>CN04XFCWTV2003AH0YJT</t>
   </si>
   <si>
-    <t xml:space="preserve">UPS </t>
+    <t>UPS</t>
   </si>
   <si>
     <t>KOBLENZ</t>
@@ -140,7 +140,7 @@
     <t>HP19XS3</t>
   </si>
   <si>
-    <t>Cargador Docking</t>
+    <t>Cargador de Docking</t>
   </si>
   <si>
     <t>LA180PM180</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Rednar García Harcía</t>
-  </si>
-  <si>
-    <t>Auxiliar de Supervision</t>
+    <t>Abraham Palayot Sanchez</t>
+  </si>
+  <si>
+    <t>Informacion Financiera</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>08/05/2025</t>
+    <t>12/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -92,6 +92,12 @@
     <t>DELL</t>
   </si>
   <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
     <t>Latitude 3520</t>
   </si>
   <si>
@@ -149,6 +155,18 @@
     <t>CN-02N6C5-LOC00-29K-9278-A01</t>
   </si>
   <si>
+    <t>Fijo</t>
+  </si>
+  <si>
+    <t>Kenwood</t>
+  </si>
+  <si>
+    <t>NX-840H-K2</t>
+  </si>
+  <si>
+    <t>B8410041</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -179,10 +197,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Abraham Palayot Sanchez</t>
-  </si>
-  <si>
-    <t>Informacion Financiera</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1018,55 +1036,55 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22" t="s">
+      <c r="A20" s="38">
+        <v>2</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="38">
-        <v>2</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="38" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="38">
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1077,17 +1095,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>33</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1098,17 +1116,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>38</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1119,97 +1137,113 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
+      <c r="A26" s="38">
+        <v>7</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
+      <c r="A27" s="38">
+        <v>8</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+      <c r="A30" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
+      <c r="A31" s="27"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
       <c r="A32" s="28" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -1220,23 +1254,22 @@
       <c r="H32" s="28"/>
       <c r="I32" s="28"/>
     </row>
-    <row r="33" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A33" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="27">
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="28" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -1247,96 +1280,101 @@
       <c r="H34" s="28"/>
       <c r="I34" s="28"/>
     </row>
-    <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="39">
-      <c r="A36" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
+    <row r="35" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A35" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="27">
+      <c r="A36" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="2"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="39">
+      <c r="A38" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="32"/>
-      <c r="B39" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="36" t="s">
-        <v>52</v>
-      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="2"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
+      <c r="G41" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="D42" s="36" t="s">
+        <v>58</v>
+      </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -1345,68 +1383,90 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="34" t="str">
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="34" t="str">
         <f>C10</f>
         <v>Juan Carlos Requena</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="34" t="str">
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+    </row>
+    <row r="46" spans="1:10" customHeight="1" ht="15">
+      <c r="A46" s="2"/>
+      <c r="B46" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="34" t="str">
         <f>C12</f>
         <v>Programador Junior</v>
       </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-    </row>
-    <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="32"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="32"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1425,23 +1485,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="G46:I46"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1463,7 +1523,13 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H19:I25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H19:I27"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -110,7 +110,13 @@
     <t>Cargador de Laptop</t>
   </si>
   <si>
+    <t>Tesla</t>
+  </si>
+  <si>
     <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
   </si>
   <si>
     <t>CN-0V2TJ7-LOC00-28C-BGDM-A00</t>
@@ -1077,14 +1083,14 @@
         <v>29</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1095,17 +1101,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1116,17 +1122,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="38" t="s">
         <v>35</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>37</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1137,17 +1143,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="38" t="s">
         <v>39</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>40</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1158,17 +1164,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1179,84 +1185,92 @@
         <v>8</v>
       </c>
       <c r="B27" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="38" t="s">
         <v>45</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>47</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
+      <c r="A28" s="38">
+        <v>9</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
+      <c r="A31" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="A32" s="27"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
@@ -1269,7 +1283,7 @@
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
       <c r="A34" s="28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
@@ -1280,171 +1294,173 @@
       <c r="H34" s="28"/>
       <c r="I34" s="28"/>
     </row>
-    <row r="35" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A35" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="27">
-      <c r="A36" s="28" t="s">
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="39">
-      <c r="A38" s="31" t="s">
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A36" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="32"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="27">
+      <c r="A37" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="15">
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="39">
+      <c r="A39" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="2"/>
+      <c r="A40" s="32"/>
       <c r="B40" s="32"/>
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+      <c r="G40" s="33"/>
       <c r="H40" s="33"/>
       <c r="I40" s="33"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="32"/>
-      <c r="B41" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="36" t="s">
+      <c r="A42" s="32"/>
+      <c r="B42" s="34" t="s">
         <v>58</v>
       </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="G42" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="36" t="s">
+        <v>60</v>
+      </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
-      <c r="B45" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="34" t="str">
-        <f>C10</f>
-        <v>Juan Carlos Requena</v>
-      </c>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
       <c r="B46" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C46" s="34"/>
       <c r="D46" s="34"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="34" t="str">
+        <f>C10</f>
+        <v>Juan Carlos Requena</v>
+      </c>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="34" t="str">
         <f>C12</f>
         <v>Programador Junior</v>
       </c>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-    </row>
-    <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
       <c r="A48" s="2"/>
@@ -1453,20 +1469,31 @@
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="32"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" customHeight="1" ht="15">
+      <c r="A50" s="32"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1485,23 +1512,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="G42:I42"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="G46:I46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="G47:I47"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1529,7 +1556,10 @@
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H19:I27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H19:I28"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
+++ b/database/controller_excel/Resguardo_Juan_Carlos_Requena.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="69">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>12/06/2025</t>
+    <t>16/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -117,6 +117,24 @@
   </si>
   <si>
     <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG0C698O</t>
+  </si>
+  <si>
+    <t>MK235</t>
+  </si>
+  <si>
+    <t>2134MR38A788</t>
   </si>
   <si>
     <t>CN-0V2TJ7-LOC00-28C-BGDM-A00</t>
@@ -1101,17 +1119,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1122,17 +1140,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="38" t="s">
-        <v>23</v>
-      </c>
       <c r="D24" s="38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1143,17 +1161,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1164,17 +1182,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1185,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B27" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="38" t="s">
         <v>44</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>23</v>
       </c>
       <c r="D27" s="38" t="s">
         <v>45</v>
@@ -1209,94 +1227,110 @@
         <v>47</v>
       </c>
       <c r="C28" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="38" t="s">
         <v>48</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>49</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
+      <c r="A29" s="38">
+        <v>10</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
+      <c r="A30" s="38">
+        <v>11</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
+      <c r="A33" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
+      <c r="A34" s="27"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
     </row>
     <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="28" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
@@ -1307,23 +1341,22 @@
       <c r="H35" s="28"/>
       <c r="I35" s="28"/>
     </row>
-    <row r="36" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A36" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="27">
+    <row r="36" spans="1:10" customHeight="1" ht="15">
+      <c r="A36" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="15">
       <c r="A37" s="28" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
@@ -1334,96 +1367,101 @@
       <c r="H37" s="28"/>
       <c r="I37" s="28"/>
     </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="39">
-      <c r="A39" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
+    <row r="38" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A38" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="27">
+      <c r="A39" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="32"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
-    </row>
-    <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="2"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+    </row>
+    <row r="41" spans="1:10" customHeight="1" ht="39">
+      <c r="A41" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="32"/>
-      <c r="B42" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="36" t="s">
-        <v>60</v>
-      </c>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
+      <c r="A44" s="32"/>
+      <c r="B44" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
+      <c r="G44" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="D45" s="36" t="s">
+        <v>66</v>
+      </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -1432,68 +1470,90 @@
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
-      <c r="B46" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="34" t="str">
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="2"/>
+      <c r="B48" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="34" t="str">
         <f>C10</f>
         <v>Juan Carlos Requena</v>
       </c>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-    </row>
-    <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="2"/>
-      <c r="B47" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="34" t="str">
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="2"/>
+      <c r="B49" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="34" t="str">
         <f>C12</f>
         <v>Programador Junior</v>
       </c>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-    </row>
-    <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-    </row>
-    <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="32"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+    </row>
+    <row r="51" spans="1:10" customHeight="1" ht="15">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:10" customHeight="1" ht="15">
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1512,23 +1572,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:I31"/>
     <mergeCell ref="A33:I33"/>
-    <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A39:I39"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="G49:I49"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1559,7 +1619,13 @@
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H19:I28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H19:I30"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>
